--- a/archive/2026-10-25/svod.xlsx
+++ b/archive/2026-10-25/svod.xlsx
@@ -603,7 +603,7 @@
     <t xml:space="preserve">34-Н2892/12</t>
   </si>
   <si>
-    <t xml:space="preserve">28-Н321512д/н</t>
+    <t xml:space="preserve">28-Н321512н</t>
   </si>
   <si>
     <t xml:space="preserve">34-Н2893/12</t>
@@ -6446,15 +6446,15 @@
       </c>
       <c r="D6" s="7" t="n">
         <f aca="false">F6+G6</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="7" t="n">
         <f aca="false">D6-C6</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F6" s="7" t="n">
         <f aca="false">SUMIFS($H6:$CG6,$H$2:$CG$2,"День")</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6" s="7" t="n">
         <f aca="false">SUMIFS($H6:$CG6,$H$2:$CG$2,"Ночь")</f>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AJ6" s="6" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$I$2:$I$970,'Исходные данные'!$D$2:$D$970,AJ$1,'Исходные данные'!$F$2:$F$970,$A6)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK6" s="6" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$J$2:$J$970,'Исходные данные'!$D$2:$D$970,AJ$1,'Исходные данные'!$F$2:$F$970,$A6)</f>
@@ -23395,15 +23395,15 @@
       </c>
       <c r="D56" s="7" t="n">
         <f aca="false">SUM(D3:D55)</f>
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E56" s="7" t="n">
         <f aca="false">SUM(E3:E55)</f>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="F56" s="7" t="n">
         <f aca="false">SUM(F3:F55)</f>
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G56" s="7" t="n">
         <f aca="false">SUM(G3:G55)</f>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="AJ56" s="10" t="n">
         <f aca="false">SUM(AJ3:AJ55)</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AK56" s="10" t="n">
         <f aca="false">SUM(AK3:AK55)</f>
@@ -23730,7 +23730,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7" t="n">
         <f aca="false">D56</f>
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
@@ -23807,7 +23807,7 @@
       <c r="AI57" s="11"/>
       <c r="AJ57" s="11" t="n">
         <f aca="false">AJ56+AK56</f>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AK57" s="11"/>
       <c r="AL57" s="11" t="n">
@@ -24883,7 +24883,7 @@
       </c>
       <c r="AD10" s="61" t="str">
         <f aca="false">IF(SUMIFS('Исходные данные'!$I$2:$I$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"",'Исходные данные'!$L$2:$L$970,"УТТ")+SUMIFS('Исходные данные'!$J$2:$J$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"",'Исходные данные'!$L$2:$L$970,"УТТ")=0,"","утт-"&amp;(SUMIFS('Исходные данные'!$I$2:$I$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"",'Исходные данные'!$L$2:$L$970,"УТТ")+SUMIFS('Исходные данные'!$J$2:$J$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"",'Исходные данные'!$L$2:$L$970,"УТТ")))</f>
-        <v>утт-7</v>
+        <v>утт-6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24916,15 +24916,15 @@
       </c>
       <c r="K11" s="46" t="n">
         <f aca="false">IFERROR(INDEX('Выход ТС'!$D:$D,MATCH($H11&amp;"",'Выход ТС'!$A:$A,0)),"")</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L11" s="47" t="n">
         <f aca="false">IFERROR(INDEX('Выход ТС'!$E:$E,MATCH($H11&amp;"",'Выход ТС'!$A:$A,0)),"")</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M11" s="48" t="n">
         <f aca="false">IFERROR(IF(INDEX('Выход ТС'!$F:$F,MATCH($H11&amp;"",'Выход ТС'!$A:$A,0))=0,"",INDEX('Выход ТС'!$F:$F,MATCH($H11&amp;"",'Выход ТС'!$A:$A,0))),"")</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N11" s="48" t="n">
         <f aca="false">IFERROR(IF(INDEX('Выход ТС'!$G:$G,MATCH($H11&amp;"",'Выход ТС'!$A:$A,0))=0,"",INDEX('Выход ТС'!$G:$G,MATCH($H11&amp;"",'Выход ТС'!$A:$A,0))),"")</f>
@@ -24992,7 +24992,7 @@
       </c>
       <c r="AD11" s="50" t="str">
         <f aca="false">IF(SUMIFS('Исходные данные'!$I$2:$I$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"")+SUMIFS('Исходные данные'!$J$2:$J$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"")=0,"",IF(SUMIFS('Исходные данные'!$J$2:$J$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"")=0,SUMIFS('Исходные данные'!$I$2:$I$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;""),IF(SUMIFS('Исходные данные'!$I$2:$I$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"")=0,"0+"&amp;SUMIFS('Исходные данные'!$J$2:$J$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"")&amp;"="&amp;SUMIFS('Исходные данные'!$J$2:$J$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;""),SUMIFS('Исходные данные'!$I$2:$I$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"")&amp;"+"&amp;SUMIFS('Исходные данные'!$J$2:$J$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"")&amp;"="&amp;(SUMIFS('Исходные данные'!$I$2:$I$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"")+SUMIFS('Исходные данные'!$J$2:$J$970,'Исходные данные'!$D$2:$D$970,AD$3,'Исходные данные'!$F$2:$F$970,$H11&amp;"")))))</f>
-        <v>4+3=7</v>
+        <v>3+3=6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34384,7 +34384,7 @@
         <v>396</v>
       </c>
       <c r="I169" s="114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J169" s="114" t="n">
         <v>1</v>

--- a/archive/2026-10-25/svod.xlsx
+++ b/archive/2026-10-25/svod.xlsx
@@ -4913,7 +4913,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:CG57"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -23960,18 +23960,18 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AD71"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="15" style="0" width="16.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="15" style="0" width="16.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28506,7 +28506,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L665"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
